--- a/apps/name-masker/selftest/樣本_名冊合成資料.xlsx
+++ b/apps/name-masker/selftest/樣本_名冊合成資料.xlsx
@@ -435,7 +435,7 @@
     </row>
     <row r="2">
       <c r="B2" t="n">
-        <v>411354043</v>
+        <v>990054043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -455,7 +455,7 @@
     </row>
     <row r="3">
       <c r="B3" t="n">
-        <v>411354044</v>
+        <v>990054044</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>411354045</t>
+          <t>990054045</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
